--- a/data/testdata.xlsx
+++ b/data/testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramal\Desktop\Problem_Bolo_Automation\Problem_Bolo\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramal\Desktop\problem bolo automation\Problem_bolo_Automation_scripts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D4C69FE-1443-4166-AE86-B460407EDEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB917DBC-207E-4E9A-AE74-B80CA797BC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="101">
   <si>
     <t>TC ID</t>
   </si>
@@ -305,13 +305,31 @@
   </si>
   <si>
     <t>View modal shows read-only country details</t>
+  </si>
+  <si>
+    <t>COUNTRY14</t>
+  </si>
+  <si>
+    <t>Public Rep Details</t>
+  </si>
+  <si>
+    <t>Step 6 of add country</t>
+  </si>
+  <si>
+    <t>uploaded files</t>
+  </si>
+  <si>
+    <t>uploading files</t>
+  </si>
+  <si>
+    <t>Public Rep files uploaded successfully</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +345,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -675,8 +699,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="33" customWidth="1"/>
+    <col min="7" max="7" width="49.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1041,22 +1074,22 @@
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>71</v>
@@ -1067,31 +1100,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>20</v>
@@ -1099,28 +1132,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>12</v>
@@ -1131,37 +1164,70 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>